--- a/Zinc/5. Statistical data analysis/Sites with several typologies/Sites_with_many_typologies.xlsx
+++ b/Zinc/5. Statistical data analysis/Sites with several typologies/Sites_with_many_typologies.xlsx
@@ -26,13 +26,13 @@
     <t xml:space="preserve">BCK0.9</t>
   </si>
   <si>
-    <t xml:space="preserve">P Tribs, Main Stem</t>
+    <t xml:space="preserve">Main Stem, P Tribs</t>
   </si>
   <si>
     <t xml:space="preserve">BSL1.1</t>
   </si>
   <si>
-    <t xml:space="preserve">P Tribs, PD Tribs, Main Stem</t>
+    <t xml:space="preserve">Main Stem, P Tribs, PD Tribs</t>
   </si>
   <si>
     <t xml:space="preserve">BSL1.2</t>
